--- a/data/irrigation_records.xlsx
+++ b/data/irrigation_records.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1505"/>
+  <dimension ref="A1:E1536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30392,11 +30392,11 @@
     </row>
     <row r="1492">
       <c r="A1492" s="2" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>DG38000</t>
+          <t>DG18000</t>
         </is>
       </c>
       <c r="C1492" t="n">
@@ -30411,11 +30411,11 @@
     </row>
     <row r="1493">
       <c r="A1493" s="2" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>DG03000</t>
+          <t>DG38000</t>
         </is>
       </c>
       <c r="C1493" t="n">
@@ -30430,11 +30430,11 @@
     </row>
     <row r="1494">
       <c r="A1494" s="2" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>DG04000</t>
+          <t>DG14000</t>
         </is>
       </c>
       <c r="C1494" t="n">
@@ -30449,11 +30449,11 @@
     </row>
     <row r="1495">
       <c r="A1495" s="2" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>DG05000</t>
+          <t>DG15000</t>
         </is>
       </c>
       <c r="C1495" t="n">
@@ -30468,11 +30468,11 @@
     </row>
     <row r="1496">
       <c r="A1496" s="2" t="n">
-        <v>46295</v>
+        <v>46292</v>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>DG02000</t>
+          <t>DG16000</t>
         </is>
       </c>
       <c r="C1496" t="n">
@@ -30487,11 +30487,11 @@
     </row>
     <row r="1497">
       <c r="A1497" s="2" t="n">
-        <v>46296</v>
+        <v>46292</v>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>DG08000</t>
+          <t>DG22000</t>
         </is>
       </c>
       <c r="C1497" t="n">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>DG14000</t>
+          <t>DG24000</t>
         </is>
       </c>
       <c r="C1498" t="n">
@@ -30525,11 +30525,11 @@
     </row>
     <row r="1499">
       <c r="A1499" s="2" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>DG15000</t>
+          <t>DG03000</t>
         </is>
       </c>
       <c r="C1499" t="n">
@@ -30544,11 +30544,11 @@
     </row>
     <row r="1500">
       <c r="A1500" s="2" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>DG16000</t>
+          <t>DG04000</t>
         </is>
       </c>
       <c r="C1500" t="n">
@@ -30563,11 +30563,11 @@
     </row>
     <row r="1501">
       <c r="A1501" s="2" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>DG18000</t>
+          <t>DG05000</t>
         </is>
       </c>
       <c r="C1501" t="n">
@@ -30582,11 +30582,11 @@
     </row>
     <row r="1502">
       <c r="A1502" s="2" t="n">
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>DG22000</t>
+          <t>DG02000</t>
         </is>
       </c>
       <c r="C1502" t="n">
@@ -30601,11 +30601,11 @@
     </row>
     <row r="1503">
       <c r="A1503" s="2" t="n">
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>DG24000</t>
+          <t>DG08000</t>
         </is>
       </c>
       <c r="C1503" t="n">
@@ -30624,7 +30624,7 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>DG20000</t>
+          <t>DG08000</t>
         </is>
       </c>
       <c r="C1504" t="n">
@@ -30638,12 +30638,12 @@
       </c>
     </row>
     <row r="1505">
-      <c r="A1505" s="3" t="n">
-        <v>46297</v>
+      <c r="A1505" s="2" t="n">
+        <v>46296</v>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>DG24000</t>
+          <t>DG20000</t>
         </is>
       </c>
       <c r="C1505" t="n">
@@ -30651,6 +30651,595 @@
       </c>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>DG01000</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1506" t="inlineStr"/>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>DG02000</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1507" t="inlineStr"/>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>DG24000</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1508" t="inlineStr"/>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>DG10000</t>
+        </is>
+      </c>
+      <c r="C1509" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1509" t="inlineStr"/>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>DG03000</t>
+        </is>
+      </c>
+      <c r="C1510" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1510" t="inlineStr"/>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>DG05000</t>
+        </is>
+      </c>
+      <c r="C1511" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1511" t="inlineStr"/>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>DG37000</t>
+        </is>
+      </c>
+      <c r="C1512" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1512" t="inlineStr"/>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>DG38000</t>
+        </is>
+      </c>
+      <c r="C1513" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1513" t="inlineStr"/>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>DG28000</t>
+        </is>
+      </c>
+      <c r="C1514" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1514" t="inlineStr"/>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>DG04000</t>
+        </is>
+      </c>
+      <c r="C1515" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1515" t="inlineStr"/>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>DG32000</t>
+        </is>
+      </c>
+      <c r="C1516" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1516" t="inlineStr"/>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>DG34000</t>
+        </is>
+      </c>
+      <c r="C1517" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1517" t="inlineStr"/>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>DG02000</t>
+        </is>
+      </c>
+      <c r="C1518" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1518" t="inlineStr"/>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>DG09000</t>
+        </is>
+      </c>
+      <c r="C1519" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1519" t="inlineStr"/>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>DG11000</t>
+        </is>
+      </c>
+      <c r="C1520" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1520" t="inlineStr"/>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>DG22000</t>
+        </is>
+      </c>
+      <c r="C1521" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1521" t="inlineStr"/>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>DG01000</t>
+        </is>
+      </c>
+      <c r="C1522" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1522" t="inlineStr"/>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>DG03000</t>
+        </is>
+      </c>
+      <c r="C1523" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1523" t="inlineStr"/>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>DG04000</t>
+        </is>
+      </c>
+      <c r="C1524" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1524" t="inlineStr"/>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>DG05000</t>
+        </is>
+      </c>
+      <c r="C1525" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1525" t="inlineStr"/>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>DG08000</t>
+        </is>
+      </c>
+      <c r="C1526" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1526" t="inlineStr"/>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>DG14000</t>
+        </is>
+      </c>
+      <c r="C1527" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1527" t="inlineStr"/>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>DG14000</t>
+        </is>
+      </c>
+      <c r="C1528" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1528" t="inlineStr"/>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>DG16000</t>
+        </is>
+      </c>
+      <c r="C1529" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1529" t="inlineStr"/>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>DG16000</t>
+        </is>
+      </c>
+      <c r="C1530" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1530" t="inlineStr"/>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>DG16000</t>
+        </is>
+      </c>
+      <c r="C1531" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1531" t="inlineStr"/>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>DG18000</t>
+        </is>
+      </c>
+      <c r="C1532" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1532" t="inlineStr"/>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>DG39000</t>
+        </is>
+      </c>
+      <c r="C1533" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1533" t="inlineStr"/>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>DG33000</t>
+        </is>
+      </c>
+      <c r="C1534" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1534" t="inlineStr"/>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>DG36000</t>
+        </is>
+      </c>
+      <c r="C1535" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1535" t="inlineStr"/>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>DG35000</t>
+        </is>
+      </c>
+      <c r="C1536" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1536" t="inlineStr"/>
+      <c r="E1536" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>

--- a/data/irrigation_records.xlsx
+++ b/data/irrigation_records.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1536"/>
+  <dimension ref="A1:E1548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30525,11 +30525,11 @@
     </row>
     <row r="1499">
       <c r="A1499" s="2" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>DG03000</t>
+          <t>DG32000</t>
         </is>
       </c>
       <c r="C1499" t="n">
@@ -30548,7 +30548,7 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>DG04000</t>
+          <t>DG03000</t>
         </is>
       </c>
       <c r="C1500" t="n">
@@ -30567,7 +30567,7 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>DG05000</t>
+          <t>DG04000</t>
         </is>
       </c>
       <c r="C1501" t="n">
@@ -30582,11 +30582,11 @@
     </row>
     <row r="1502">
       <c r="A1502" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>DG02000</t>
+          <t>DG05000</t>
         </is>
       </c>
       <c r="C1502" t="n">
@@ -30601,11 +30601,11 @@
     </row>
     <row r="1503">
       <c r="A1503" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>DG08000</t>
+          <t>DG28000</t>
         </is>
       </c>
       <c r="C1503" t="n">
@@ -30620,11 +30620,11 @@
     </row>
     <row r="1504">
       <c r="A1504" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>DG08000</t>
+          <t>DG31000</t>
         </is>
       </c>
       <c r="C1504" t="n">
@@ -30639,11 +30639,11 @@
     </row>
     <row r="1505">
       <c r="A1505" s="2" t="n">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>DG20000</t>
+          <t>DG39000</t>
         </is>
       </c>
       <c r="C1505" t="n">
@@ -30658,11 +30658,11 @@
     </row>
     <row r="1506">
       <c r="A1506" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>DG01000</t>
+          <t>DG02000</t>
         </is>
       </c>
       <c r="C1506" t="n">
@@ -30677,11 +30677,11 @@
     </row>
     <row r="1507">
       <c r="A1507" s="2" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>DG02000</t>
+          <t>DG08000</t>
         </is>
       </c>
       <c r="C1507" t="n">
@@ -30696,11 +30696,11 @@
     </row>
     <row r="1508">
       <c r="A1508" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>DG24000</t>
+          <t>DG08000</t>
         </is>
       </c>
       <c r="C1508" t="n">
@@ -30715,11 +30715,11 @@
     </row>
     <row r="1509">
       <c r="A1509" s="2" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>DG10000</t>
+          <t>DG20000</t>
         </is>
       </c>
       <c r="C1509" t="n">
@@ -30734,11 +30734,11 @@
     </row>
     <row r="1510">
       <c r="A1510" s="2" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>DG03000</t>
+          <t>DG01000</t>
         </is>
       </c>
       <c r="C1510" t="n">
@@ -30753,11 +30753,11 @@
     </row>
     <row r="1511">
       <c r="A1511" s="2" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>DG05000</t>
+          <t>DG02000</t>
         </is>
       </c>
       <c r="C1511" t="n">
@@ -30772,11 +30772,11 @@
     </row>
     <row r="1512">
       <c r="A1512" s="2" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>DG37000</t>
+          <t>DG24000</t>
         </is>
       </c>
       <c r="C1512" t="n">
@@ -30791,11 +30791,11 @@
     </row>
     <row r="1513">
       <c r="A1513" s="2" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>DG38000</t>
+          <t>DG10000</t>
         </is>
       </c>
       <c r="C1513" t="n">
@@ -30810,11 +30810,11 @@
     </row>
     <row r="1514">
       <c r="A1514" s="2" t="n">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>DG28000</t>
+          <t>DG03000</t>
         </is>
       </c>
       <c r="C1514" t="n">
@@ -30829,11 +30829,11 @@
     </row>
     <row r="1515">
       <c r="A1515" s="2" t="n">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>DG04000</t>
+          <t>DG05000</t>
         </is>
       </c>
       <c r="C1515" t="n">
@@ -30848,11 +30848,11 @@
     </row>
     <row r="1516">
       <c r="A1516" s="2" t="n">
-        <v>46303</v>
+        <v>46301</v>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>DG32000</t>
+          <t>DG37000</t>
         </is>
       </c>
       <c r="C1516" t="n">
@@ -30867,11 +30867,11 @@
     </row>
     <row r="1517">
       <c r="A1517" s="2" t="n">
-        <v>46303</v>
+        <v>46301</v>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>DG34000</t>
+          <t>DG38000</t>
         </is>
       </c>
       <c r="C1517" t="n">
@@ -30886,11 +30886,11 @@
     </row>
     <row r="1518">
       <c r="A1518" s="2" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>DG02000</t>
+          <t>DG04000</t>
         </is>
       </c>
       <c r="C1518" t="n">
@@ -30909,7 +30909,7 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>DG09000</t>
+          <t>DG28000</t>
         </is>
       </c>
       <c r="C1519" t="n">
@@ -30924,11 +30924,11 @@
     </row>
     <row r="1520">
       <c r="A1520" s="2" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>DG11000</t>
+          <t>DG32000</t>
         </is>
       </c>
       <c r="C1520" t="n">
@@ -30943,11 +30943,11 @@
     </row>
     <row r="1521">
       <c r="A1521" s="2" t="n">
-        <v>46309</v>
+        <v>46303</v>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>DG22000</t>
+          <t>DG34000</t>
         </is>
       </c>
       <c r="C1521" t="n">
@@ -30962,11 +30962,11 @@
     </row>
     <row r="1522">
       <c r="A1522" s="2" t="n">
-        <v>46305</v>
+        <v>46303</v>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>DG01000</t>
+          <t>DG02000</t>
         </is>
       </c>
       <c r="C1522" t="n">
@@ -30981,11 +30981,11 @@
     </row>
     <row r="1523">
       <c r="A1523" s="2" t="n">
-        <v>46306</v>
+        <v>46303</v>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>DG03000</t>
+          <t>DG09000</t>
         </is>
       </c>
       <c r="C1523" t="n">
@@ -31000,11 +31000,11 @@
     </row>
     <row r="1524">
       <c r="A1524" s="2" t="n">
-        <v>46309</v>
+        <v>46304</v>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>DG04000</t>
+          <t>DG11000</t>
         </is>
       </c>
       <c r="C1524" t="n">
@@ -31019,11 +31019,11 @@
     </row>
     <row r="1525">
       <c r="A1525" s="2" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>DG05000</t>
+          <t>DG22000</t>
         </is>
       </c>
       <c r="C1525" t="n">
@@ -31038,11 +31038,11 @@
     </row>
     <row r="1526">
       <c r="A1526" s="2" t="n">
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>DG08000</t>
+          <t>DG01000</t>
         </is>
       </c>
       <c r="C1526" t="n">
@@ -31057,11 +31057,11 @@
     </row>
     <row r="1527">
       <c r="A1527" s="2" t="n">
-        <v>46298</v>
+        <v>46306</v>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>DG14000</t>
+          <t>DG03000</t>
         </is>
       </c>
       <c r="C1527" t="n">
@@ -31076,11 +31076,11 @@
     </row>
     <row r="1528">
       <c r="A1528" s="2" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>DG14000</t>
+          <t>DG04000</t>
         </is>
       </c>
       <c r="C1528" t="n">
@@ -31095,11 +31095,11 @@
     </row>
     <row r="1529">
       <c r="A1529" s="2" t="n">
-        <v>46298</v>
+        <v>46306</v>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>DG16000</t>
+          <t>DG05000</t>
         </is>
       </c>
       <c r="C1529" t="n">
@@ -31114,11 +31114,11 @@
     </row>
     <row r="1530">
       <c r="A1530" s="2" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>DG16000</t>
+          <t>DG08000</t>
         </is>
       </c>
       <c r="C1530" t="n">
@@ -31133,11 +31133,11 @@
     </row>
     <row r="1531">
       <c r="A1531" s="2" t="n">
-        <v>46309</v>
+        <v>46298</v>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>DG16000</t>
+          <t>DG14000</t>
         </is>
       </c>
       <c r="C1531" t="n">
@@ -31152,11 +31152,11 @@
     </row>
     <row r="1532">
       <c r="A1532" s="2" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>DG18000</t>
+          <t>DG14000</t>
         </is>
       </c>
       <c r="C1532" t="n">
@@ -31171,11 +31171,11 @@
     </row>
     <row r="1533">
       <c r="A1533" s="2" t="n">
-        <v>46308</v>
+        <v>46298</v>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>DG39000</t>
+          <t>DG16000</t>
         </is>
       </c>
       <c r="C1533" t="n">
@@ -31190,11 +31190,11 @@
     </row>
     <row r="1534">
       <c r="A1534" s="2" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>DG33000</t>
+          <t>DG16000</t>
         </is>
       </c>
       <c r="C1534" t="n">
@@ -31209,11 +31209,11 @@
     </row>
     <row r="1535">
       <c r="A1535" s="2" t="n">
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>DG36000</t>
+          <t>DG16000</t>
         </is>
       </c>
       <c r="C1535" t="n">
@@ -31227,12 +31227,12 @@
       </c>
     </row>
     <row r="1536">
-      <c r="A1536" s="3" t="n">
-        <v>46308</v>
+      <c r="A1536" s="2" t="n">
+        <v>46305</v>
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>DG35000</t>
+          <t>DG18000</t>
         </is>
       </c>
       <c r="C1536" t="n">
@@ -31240,6 +31240,234 @@
       </c>
       <c r="D1536" t="inlineStr"/>
       <c r="E1536" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>DG33000</t>
+        </is>
+      </c>
+      <c r="C1537" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1537" t="inlineStr"/>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>DG36000</t>
+        </is>
+      </c>
+      <c r="C1538" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1538" t="inlineStr"/>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>DG35000</t>
+        </is>
+      </c>
+      <c r="C1539" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1539" t="inlineStr"/>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>DG13000</t>
+        </is>
+      </c>
+      <c r="C1540" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1540" t="inlineStr"/>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>DG14000</t>
+        </is>
+      </c>
+      <c r="C1541" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1541" t="inlineStr"/>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>DG15000</t>
+        </is>
+      </c>
+      <c r="C1542" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1542" t="inlineStr"/>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>DG20000</t>
+        </is>
+      </c>
+      <c r="C1543" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1543" t="inlineStr"/>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>DG20000</t>
+        </is>
+      </c>
+      <c r="C1544" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1544" t="inlineStr"/>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>DG26000</t>
+        </is>
+      </c>
+      <c r="C1545" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1545" t="inlineStr"/>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>DG31000</t>
+        </is>
+      </c>
+      <c r="C1546" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1546" t="inlineStr"/>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>DG35000</t>
+        </is>
+      </c>
+      <c r="C1547" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1547" t="inlineStr"/>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>DG39000</t>
+        </is>
+      </c>
+      <c r="C1548" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1548" t="inlineStr"/>
+      <c r="E1548" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>

--- a/data/irrigation_records.xlsx
+++ b/data/irrigation_records.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1548"/>
+  <dimension ref="A1:E1549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30810,11 +30810,11 @@
     </row>
     <row r="1514">
       <c r="A1514" s="2" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>DG03000</t>
+          <t>DG14000</t>
         </is>
       </c>
       <c r="C1514" t="n">
@@ -30829,11 +30829,11 @@
     </row>
     <row r="1515">
       <c r="A1515" s="2" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>DG05000</t>
+          <t>DG16000</t>
         </is>
       </c>
       <c r="C1515" t="n">
@@ -30848,11 +30848,11 @@
     </row>
     <row r="1516">
       <c r="A1516" s="2" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>DG37000</t>
+          <t>DG26000</t>
         </is>
       </c>
       <c r="C1516" t="n">
@@ -30867,11 +30867,11 @@
     </row>
     <row r="1517">
       <c r="A1517" s="2" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>DG38000</t>
+          <t>DG35000</t>
         </is>
       </c>
       <c r="C1517" t="n">
@@ -30886,11 +30886,11 @@
     </row>
     <row r="1518">
       <c r="A1518" s="2" t="n">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>DG04000</t>
+          <t>DG03000</t>
         </is>
       </c>
       <c r="C1518" t="n">
@@ -30905,11 +30905,11 @@
     </row>
     <row r="1519">
       <c r="A1519" s="2" t="n">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>DG28000</t>
+          <t>DG05000</t>
         </is>
       </c>
       <c r="C1519" t="n">
@@ -30924,11 +30924,11 @@
     </row>
     <row r="1520">
       <c r="A1520" s="2" t="n">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>DG32000</t>
+          <t>DG13000</t>
         </is>
       </c>
       <c r="C1520" t="n">
@@ -30943,11 +30943,11 @@
     </row>
     <row r="1521">
       <c r="A1521" s="2" t="n">
-        <v>46303</v>
+        <v>46301</v>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>DG34000</t>
+          <t>DG37000</t>
         </is>
       </c>
       <c r="C1521" t="n">
@@ -30962,11 +30962,11 @@
     </row>
     <row r="1522">
       <c r="A1522" s="2" t="n">
-        <v>46303</v>
+        <v>46301</v>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>DG02000</t>
+          <t>DG38000</t>
         </is>
       </c>
       <c r="C1522" t="n">
@@ -30981,11 +30981,11 @@
     </row>
     <row r="1523">
       <c r="A1523" s="2" t="n">
-        <v>46303</v>
+        <v>46301</v>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>DG09000</t>
+          <t>DG15000</t>
         </is>
       </c>
       <c r="C1523" t="n">
@@ -31000,11 +31000,11 @@
     </row>
     <row r="1524">
       <c r="A1524" s="2" t="n">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>DG11000</t>
+          <t>DG04000</t>
         </is>
       </c>
       <c r="C1524" t="n">
@@ -31019,11 +31019,11 @@
     </row>
     <row r="1525">
       <c r="A1525" s="2" t="n">
-        <v>46309</v>
+        <v>46302</v>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>DG22000</t>
+          <t>DG20000</t>
         </is>
       </c>
       <c r="C1525" t="n">
@@ -31038,11 +31038,11 @@
     </row>
     <row r="1526">
       <c r="A1526" s="2" t="n">
-        <v>46305</v>
+        <v>46303</v>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>DG01000</t>
+          <t>DG28000</t>
         </is>
       </c>
       <c r="C1526" t="n">
@@ -31057,11 +31057,11 @@
     </row>
     <row r="1527">
       <c r="A1527" s="2" t="n">
-        <v>46306</v>
+        <v>46303</v>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>DG03000</t>
+          <t>DG32000</t>
         </is>
       </c>
       <c r="C1527" t="n">
@@ -31076,11 +31076,11 @@
     </row>
     <row r="1528">
       <c r="A1528" s="2" t="n">
-        <v>46309</v>
+        <v>46303</v>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>DG04000</t>
+          <t>DG34000</t>
         </is>
       </c>
       <c r="C1528" t="n">
@@ -31095,11 +31095,11 @@
     </row>
     <row r="1529">
       <c r="A1529" s="2" t="n">
-        <v>46306</v>
+        <v>46303</v>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>DG05000</t>
+          <t>DG02000</t>
         </is>
       </c>
       <c r="C1529" t="n">
@@ -31114,11 +31114,11 @@
     </row>
     <row r="1530">
       <c r="A1530" s="2" t="n">
-        <v>46307</v>
+        <v>46303</v>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>DG08000</t>
+          <t>DG09000</t>
         </is>
       </c>
       <c r="C1530" t="n">
@@ -31133,11 +31133,11 @@
     </row>
     <row r="1531">
       <c r="A1531" s="2" t="n">
-        <v>46298</v>
+        <v>46304</v>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>DG14000</t>
+          <t>DG11000</t>
         </is>
       </c>
       <c r="C1531" t="n">
@@ -31171,7 +31171,7 @@
     </row>
     <row r="1533">
       <c r="A1533" s="2" t="n">
-        <v>46298</v>
+        <v>46304</v>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
@@ -31190,11 +31190,11 @@
     </row>
     <row r="1534">
       <c r="A1534" s="2" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>DG16000</t>
+          <t>DG01000</t>
         </is>
       </c>
       <c r="C1534" t="n">
@@ -31209,11 +31209,11 @@
     </row>
     <row r="1535">
       <c r="A1535" s="2" t="n">
-        <v>46309</v>
+        <v>46305</v>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>DG16000</t>
+          <t>DG18000</t>
         </is>
       </c>
       <c r="C1535" t="n">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>DG18000</t>
+          <t>DG33000</t>
         </is>
       </c>
       <c r="C1536" t="n">
@@ -31251,7 +31251,7 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>DG33000</t>
+          <t>DG36000</t>
         </is>
       </c>
       <c r="C1537" t="n">
@@ -31266,11 +31266,11 @@
     </row>
     <row r="1538">
       <c r="A1538" s="2" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>DG36000</t>
+          <t>DG03000</t>
         </is>
       </c>
       <c r="C1538" t="n">
@@ -31285,11 +31285,11 @@
     </row>
     <row r="1539">
       <c r="A1539" s="2" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>DG35000</t>
+          <t>DG05000</t>
         </is>
       </c>
       <c r="C1539" t="n">
@@ -31304,11 +31304,11 @@
     </row>
     <row r="1540">
       <c r="A1540" s="2" t="n">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>DG13000</t>
+          <t>DG08000</t>
         </is>
       </c>
       <c r="C1540" t="n">
@@ -31323,11 +31323,11 @@
     </row>
     <row r="1541">
       <c r="A1541" s="2" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>DG14000</t>
+          <t>DG35000</t>
         </is>
       </c>
       <c r="C1541" t="n">
@@ -31342,11 +31342,11 @@
     </row>
     <row r="1542">
       <c r="A1542" s="2" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>DG15000</t>
+          <t>DG31000</t>
         </is>
       </c>
       <c r="C1542" t="n">
@@ -31361,11 +31361,11 @@
     </row>
     <row r="1543">
       <c r="A1543" s="2" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>DG20000</t>
+          <t>DG22000</t>
         </is>
       </c>
       <c r="C1543" t="n">
@@ -31384,7 +31384,7 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>DG20000</t>
+          <t>DG04000</t>
         </is>
       </c>
       <c r="C1544" t="n">
@@ -31399,11 +31399,11 @@
     </row>
     <row r="1545">
       <c r="A1545" s="2" t="n">
-        <v>46298</v>
+        <v>46309</v>
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>DG26000</t>
+          <t>DG16000</t>
         </is>
       </c>
       <c r="C1545" t="n">
@@ -31418,11 +31418,11 @@
     </row>
     <row r="1546">
       <c r="A1546" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>DG31000</t>
+          <t>DG20000</t>
         </is>
       </c>
       <c r="C1546" t="n">
@@ -31437,11 +31437,11 @@
     </row>
     <row r="1547">
       <c r="A1547" s="2" t="n">
-        <v>46298</v>
+        <v>46309</v>
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>DG35000</t>
+          <t>DG39000</t>
         </is>
       </c>
       <c r="C1547" t="n">
@@ -31455,12 +31455,12 @@
       </c>
     </row>
     <row r="1548">
-      <c r="A1548" s="3" t="n">
-        <v>46309</v>
+      <c r="A1548" s="2" t="n">
+        <v>46311</v>
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>DG39000</t>
+          <t>DG14000</t>
         </is>
       </c>
       <c r="C1548" t="n">
@@ -31468,6 +31468,25 @@
       </c>
       <c r="D1548" t="inlineStr"/>
       <c r="E1548" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>DG17000</t>
+        </is>
+      </c>
+      <c r="C1549" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1549" t="inlineStr"/>
+      <c r="E1549" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>

--- a/data/irrigation_records.xlsx
+++ b/data/irrigation_records.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1549"/>
+  <dimension ref="A1:E1567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31474,7 +31474,7 @@
       </c>
     </row>
     <row r="1549">
-      <c r="A1549" s="3" t="n">
+      <c r="A1549" s="2" t="n">
         <v>46312</v>
       </c>
       <c r="B1549" t="inlineStr">
@@ -31487,6 +31487,348 @@
       </c>
       <c r="D1549" t="inlineStr"/>
       <c r="E1549" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>DG01000</t>
+        </is>
+      </c>
+      <c r="C1550" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1550" t="inlineStr"/>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>DG02000</t>
+        </is>
+      </c>
+      <c r="C1551" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1551" t="inlineStr"/>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>DG03000</t>
+        </is>
+      </c>
+      <c r="C1552" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1552" t="inlineStr"/>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>DG05000</t>
+        </is>
+      </c>
+      <c r="C1553" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1553" t="inlineStr"/>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>DG06000</t>
+        </is>
+      </c>
+      <c r="C1554" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1554" t="inlineStr"/>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>DG07000</t>
+        </is>
+      </c>
+      <c r="C1555" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1555" t="inlineStr"/>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>DG37000</t>
+        </is>
+      </c>
+      <c r="C1556" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1556" t="inlineStr"/>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>DG38000</t>
+        </is>
+      </c>
+      <c r="C1557" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1557" t="inlineStr"/>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>DG16000</t>
+        </is>
+      </c>
+      <c r="C1558" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1558" t="inlineStr"/>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>DG17000</t>
+        </is>
+      </c>
+      <c r="C1559" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1559" t="inlineStr"/>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>DG26000</t>
+        </is>
+      </c>
+      <c r="C1560" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1560" t="inlineStr"/>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>DG27000</t>
+        </is>
+      </c>
+      <c r="C1561" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1561" t="inlineStr"/>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>DG28000</t>
+        </is>
+      </c>
+      <c r="C1562" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1562" t="inlineStr"/>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>DG29000</t>
+        </is>
+      </c>
+      <c r="C1563" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1563" t="inlineStr"/>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>DG30000</t>
+        </is>
+      </c>
+      <c r="C1564" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1564" t="inlineStr"/>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>DG32000</t>
+        </is>
+      </c>
+      <c r="C1565" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1565" t="inlineStr"/>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>DG19000</t>
+        </is>
+      </c>
+      <c r="C1566" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1566" t="inlineStr"/>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>DG10000</t>
+        </is>
+      </c>
+      <c r="C1567" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1567" t="inlineStr"/>
+      <c r="E1567" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>

--- a/data/irrigation_records.xlsx
+++ b/data/irrigation_records.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1567"/>
+  <dimension ref="A1:E1595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31475,11 +31475,11 @@
     </row>
     <row r="1549">
       <c r="A1549" s="2" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>DG17000</t>
+          <t>DG03000</t>
         </is>
       </c>
       <c r="C1549" t="n">
@@ -31494,11 +31494,11 @@
     </row>
     <row r="1550">
       <c r="A1550" s="2" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>DG01000</t>
+          <t>DG37000</t>
         </is>
       </c>
       <c r="C1550" t="n">
@@ -31513,11 +31513,11 @@
     </row>
     <row r="1551">
       <c r="A1551" s="2" t="n">
-        <v>46313</v>
+        <v>46311</v>
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>DG02000</t>
+          <t>DG38000</t>
         </is>
       </c>
       <c r="C1551" t="n">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>DG03000</t>
+          <t>DG28000</t>
         </is>
       </c>
       <c r="C1552" t="n">
@@ -31551,11 +31551,11 @@
     </row>
     <row r="1553">
       <c r="A1553" s="2" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>DG05000</t>
+          <t>DG10000</t>
         </is>
       </c>
       <c r="C1553" t="n">
@@ -31570,11 +31570,11 @@
     </row>
     <row r="1554">
       <c r="A1554" s="2" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>DG06000</t>
+          <t>DG17000</t>
         </is>
       </c>
       <c r="C1554" t="n">
@@ -31589,11 +31589,11 @@
     </row>
     <row r="1555">
       <c r="A1555" s="2" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>DG07000</t>
+          <t>DG05000</t>
         </is>
       </c>
       <c r="C1555" t="n">
@@ -31608,11 +31608,11 @@
     </row>
     <row r="1556">
       <c r="A1556" s="2" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>DG37000</t>
+          <t>DG30000</t>
         </is>
       </c>
       <c r="C1556" t="n">
@@ -31627,11 +31627,11 @@
     </row>
     <row r="1557">
       <c r="A1557" s="2" t="n">
-        <v>46311</v>
+        <v>46313</v>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>DG38000</t>
+          <t>DG02000</t>
         </is>
       </c>
       <c r="C1557" t="n">
@@ -31646,11 +31646,11 @@
     </row>
     <row r="1558">
       <c r="A1558" s="2" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>DG16000</t>
+          <t>DG27000</t>
         </is>
       </c>
       <c r="C1558" t="n">
@@ -31665,11 +31665,11 @@
     </row>
     <row r="1559">
       <c r="A1559" s="2" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>DG17000</t>
+          <t>DG06000</t>
         </is>
       </c>
       <c r="C1559" t="n">
@@ -31688,7 +31688,7 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>DG26000</t>
+          <t>DG01000</t>
         </is>
       </c>
       <c r="C1560" t="n">
@@ -31703,11 +31703,11 @@
     </row>
     <row r="1561">
       <c r="A1561" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>DG27000</t>
+          <t>DG16000</t>
         </is>
       </c>
       <c r="C1561" t="n">
@@ -31722,11 +31722,11 @@
     </row>
     <row r="1562">
       <c r="A1562" s="2" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>DG28000</t>
+          <t>DG26000</t>
         </is>
       </c>
       <c r="C1562" t="n">
@@ -31741,11 +31741,11 @@
     </row>
     <row r="1563">
       <c r="A1563" s="2" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>DG29000</t>
+          <t>DG32000</t>
         </is>
       </c>
       <c r="C1563" t="n">
@@ -31760,11 +31760,11 @@
     </row>
     <row r="1564">
       <c r="A1564" s="2" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>DG30000</t>
+          <t>DG19000</t>
         </is>
       </c>
       <c r="C1564" t="n">
@@ -31779,11 +31779,11 @@
     </row>
     <row r="1565">
       <c r="A1565" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>DG32000</t>
+          <t>DG07000</t>
         </is>
       </c>
       <c r="C1565" t="n">
@@ -31802,7 +31802,7 @@
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>DG19000</t>
+          <t>DG29000</t>
         </is>
       </c>
       <c r="C1566" t="n">
@@ -31816,12 +31816,12 @@
       </c>
     </row>
     <row r="1567">
-      <c r="A1567" s="3" t="n">
-        <v>46311</v>
+      <c r="A1567" s="2" t="n">
+        <v>46315</v>
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>DG10000</t>
+          <t>DG36000</t>
         </is>
       </c>
       <c r="C1567" t="n">
@@ -31829,6 +31829,538 @@
       </c>
       <c r="D1567" t="inlineStr"/>
       <c r="E1567" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>DG33000</t>
+        </is>
+      </c>
+      <c r="C1568" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1568" t="inlineStr"/>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>DG14000</t>
+        </is>
+      </c>
+      <c r="C1569" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1569" t="inlineStr"/>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>DG03000</t>
+        </is>
+      </c>
+      <c r="C1570" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1570" t="inlineStr"/>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>DG04000</t>
+        </is>
+      </c>
+      <c r="C1571" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1571" t="inlineStr"/>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>DG25000</t>
+        </is>
+      </c>
+      <c r="C1572" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1572" t="inlineStr"/>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>DG12000</t>
+        </is>
+      </c>
+      <c r="C1573" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1573" t="inlineStr"/>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>DG34000</t>
+        </is>
+      </c>
+      <c r="C1574" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1574" t="inlineStr"/>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>DG39000</t>
+        </is>
+      </c>
+      <c r="C1575" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1575" t="inlineStr"/>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>DG05000</t>
+        </is>
+      </c>
+      <c r="C1576" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1576" t="inlineStr"/>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>DG08000</t>
+        </is>
+      </c>
+      <c r="C1577" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1577" t="inlineStr"/>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>DG36000</t>
+        </is>
+      </c>
+      <c r="C1578" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1578" t="inlineStr"/>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>DG27000</t>
+        </is>
+      </c>
+      <c r="C1579" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1579" t="inlineStr"/>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>DG35000</t>
+        </is>
+      </c>
+      <c r="C1580" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1580" t="inlineStr"/>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>DG02000</t>
+        </is>
+      </c>
+      <c r="C1581" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1581" t="inlineStr"/>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>DG13000</t>
+        </is>
+      </c>
+      <c r="C1582" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1582" t="inlineStr"/>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>DG16000</t>
+        </is>
+      </c>
+      <c r="C1583" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1583" t="inlineStr"/>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>DG18000</t>
+        </is>
+      </c>
+      <c r="C1584" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1584" t="inlineStr"/>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>DG20000</t>
+        </is>
+      </c>
+      <c r="C1585" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1585" t="inlineStr"/>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>DG24000</t>
+        </is>
+      </c>
+      <c r="C1586" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1586" t="inlineStr"/>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>DG20000</t>
+        </is>
+      </c>
+      <c r="C1587" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1587" t="inlineStr"/>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>DG19000</t>
+        </is>
+      </c>
+      <c r="C1588" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1588" t="inlineStr"/>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>DG11000</t>
+        </is>
+      </c>
+      <c r="C1589" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1589" t="inlineStr"/>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>DG31000</t>
+        </is>
+      </c>
+      <c r="C1590" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1590" t="inlineStr"/>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>DG39000</t>
+        </is>
+      </c>
+      <c r="C1591" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1591" t="inlineStr"/>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="2" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>DG07000</t>
+        </is>
+      </c>
+      <c r="C1592" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1592" t="inlineStr"/>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>DG29000</t>
+        </is>
+      </c>
+      <c r="C1593" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1593" t="inlineStr"/>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>DG32000</t>
+        </is>
+      </c>
+      <c r="C1594" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1594" t="inlineStr"/>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>DG17000</t>
+        </is>
+      </c>
+      <c r="C1595" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1595" t="inlineStr"/>
+      <c r="E1595" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>
